--- a/data/trans_dic/P36$fruta-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P36$fruta-Estudios-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que desayuna, al menos, fruta o zumo</t>
+          <t>Población que desayuna, al menos, fruta o zumo (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,78; 7,75</t>
+          <t>4,84; 7,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,29; 11,14</t>
+          <t>6,99; 10,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,56; 10,42</t>
+          <t>6,37; 10,36</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,64; 8,61</t>
+          <t>5,7; 8,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,38; 11,63</t>
+          <t>8,5; 11,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,32; 11,16</t>
+          <t>7,21; 10,98</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,66; 7,87</t>
+          <t>5,67; 7,74</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,31; 10,92</t>
+          <t>8,23; 10,83</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,41; 10,12</t>
+          <t>7,46; 10,29</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,51; 9,29</t>
+          <t>6,63; 9,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,95; 13,99</t>
+          <t>10,8; 13,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,41; 15,41</t>
+          <t>12,38; 15,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,57; 13,87</t>
+          <t>10,66; 13,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,53; 14,7</t>
+          <t>11,33; 14,82</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,64; 15,96</t>
+          <t>12,76; 15,86</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,88; 10,98</t>
+          <t>8,9; 11,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,55; 13,86</t>
+          <t>11,5; 13,62</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12,97; 15,25</t>
+          <t>13,05; 15,18</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,65; 15,76</t>
+          <t>9,84; 16,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,12; 21,36</t>
+          <t>13,85; 21,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,96; 19,61</t>
+          <t>13,18; 19,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,25; 19,44</t>
+          <t>12,34; 19,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15,18; 22,59</t>
+          <t>14,73; 22,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,24; 20,92</t>
+          <t>14,34; 20,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,84; 16,35</t>
+          <t>11,84; 16,11</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15,2; 20,68</t>
+          <t>15,47; 20,75</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14,66; 19,42</t>
+          <t>14,62; 19,33</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,17; 9,19</t>
+          <t>7,11; 9,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,91; 13,23</t>
+          <t>10,91; 13,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,8; 14,15</t>
+          <t>11,83; 14,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,66; 11,82</t>
+          <t>9,54; 11,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,55; 13,71</t>
+          <t>11,47; 13,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,17; 14,48</t>
+          <t>12,13; 14,41</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,72; 10,18</t>
+          <t>8,63; 10,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,45; 13,13</t>
+          <t>11,51; 13,17</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>12,35; 14,01</t>
+          <t>12,35; 13,99</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que desayuna, al menos, fruta o zumo</t>
+          <t>Población que desayuna, al menos, fruta o zumo (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>49084; 79683</t>
+          <t>49788; 81110</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>70909; 108374</t>
+          <t>67951; 105299</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>49384; 78449</t>
+          <t>47974; 77978</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>74030; 113000</t>
+          <t>74834; 110494</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>111885; 155402</t>
+          <t>113525; 157483</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>72732; 110824</t>
+          <t>71584; 109037</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>132416; 184274</t>
+          <t>132649; 181229</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>191939; 252176</t>
+          <t>189979; 249970</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>129351; 176645</t>
+          <t>130202; 179689</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>110137; 157250</t>
+          <t>112230; 158636</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>214691; 274428</t>
+          <t>211815; 271700</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>257409; 319548</t>
+          <t>256870; 317722</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>167542; 219969</t>
+          <t>169040; 220069</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>202418; 257895</t>
+          <t>198846; 260126</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>251140; 317015</t>
+          <t>253496; 314966</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>291186; 359871</t>
+          <t>291855; 360430</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>429018; 514987</t>
+          <t>427332; 506085</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>526835; 619239</t>
+          <t>530041; 616319</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>53015; 86605</t>
+          <t>54085; 88940</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>67807; 102571</t>
+          <t>66508; 102675</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>70903; 107268</t>
+          <t>72083; 108917</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>58356; 92592</t>
+          <t>58777; 90631</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>69460; 103350</t>
+          <t>67402; 104484</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>78215; 114864</t>
+          <t>78722; 114762</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>121455; 167738</t>
+          <t>121458; 165267</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>142551; 193914</t>
+          <t>145049; 194569</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>160711; 212816</t>
+          <t>160253; 211878</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>234573; 300452</t>
+          <t>232577; 300228</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>372518; 451506</t>
+          <t>372430; 452990</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>397952; 477383</t>
+          <t>399092; 477614</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>326152; 398925</t>
+          <t>321891; 392999</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>409789; 486565</t>
+          <t>407098; 488123</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>429618; 510955</t>
+          <t>427892; 508433</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>579619; 676510</t>
+          <t>573255; 671909</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>796988; 914276</t>
+          <t>801499; 916580</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>852752; 967373</t>
+          <t>852422; 965569</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P36$fruta-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P36$fruta-Estudios-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,84; 7,89</t>
+          <t>4,66; 7,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,99; 10,83</t>
+          <t>7,14; 11,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,37; 10,36</t>
+          <t>6,27; 10,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,7; 8,41</t>
+          <t>5,69; 8,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,5; 11,79</t>
+          <t>8,42; 11,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,21; 10,98</t>
+          <t>7,55; 11,28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,67; 7,74</t>
+          <t>5,71; 7,76</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,23; 10,83</t>
+          <t>8,37; 10,82</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,46; 10,29</t>
+          <t>7,32; 10,16</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,63; 9,37</t>
+          <t>6,52; 9,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,8; 13,85</t>
+          <t>10,88; 13,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,38; 15,32</t>
+          <t>12,49; 15,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,66; 13,88</t>
+          <t>10,55; 13,84</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,33; 14,82</t>
+          <t>11,48; 14,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,76; 15,86</t>
+          <t>12,68; 15,92</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,9; 11,0</t>
+          <t>8,89; 11,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,5; 13,62</t>
+          <t>11,45; 13,77</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,05; 15,18</t>
+          <t>12,96; 15,21</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,84; 16,18</t>
+          <t>9,81; 15,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,85; 21,38</t>
+          <t>13,84; 21,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,18; 19,92</t>
+          <t>12,84; 19,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,34; 19,02</t>
+          <t>12,47; 19,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,73; 22,84</t>
+          <t>14,92; 23,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,34; 20,9</t>
+          <t>14,25; 20,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,84; 16,11</t>
+          <t>11,56; 16,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15,47; 20,75</t>
+          <t>15,26; 20,85</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14,62; 19,33</t>
+          <t>14,56; 19,3</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,11; 9,18</t>
+          <t>7,12; 9,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,91; 13,27</t>
+          <t>10,84; 13,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,83; 14,16</t>
+          <t>11,93; 14,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,54; 11,64</t>
+          <t>9,69; 11,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,47; 13,76</t>
+          <t>11,48; 13,74</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,13; 14,41</t>
+          <t>12,29; 14,56</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,63; 10,11</t>
+          <t>8,66; 10,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,51; 13,17</t>
+          <t>11,48; 13,06</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>12,35; 13,99</t>
+          <t>12,27; 13,93</t>
         </is>
       </c>
     </row>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>49788; 81110</t>
+          <t>47928; 80102</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>67951; 105299</t>
+          <t>69487; 107165</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>47974; 77978</t>
+          <t>47211; 76701</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>74834; 110494</t>
+          <t>74782; 112317</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>113525; 157483</t>
+          <t>112412; 156932</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>71584; 109037</t>
+          <t>74999; 112044</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>132649; 181229</t>
+          <t>133657; 181708</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>189979; 249970</t>
+          <t>193295; 249719</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>130202; 179689</t>
+          <t>127817; 177349</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>112230; 158636</t>
+          <t>110361; 157353</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>211815; 271700</t>
+          <t>213300; 270220</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>256870; 317722</t>
+          <t>259121; 322969</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>169040; 220069</t>
+          <t>167220; 219398</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>198846; 260126</t>
+          <t>201431; 260338</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>253496; 314966</t>
+          <t>251901; 316190</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>291855; 360430</t>
+          <t>291450; 360689</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>427332; 506085</t>
+          <t>425576; 511518</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>530041; 616319</t>
+          <t>526097; 617655</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>54085; 88940</t>
+          <t>53918; 87111</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>66508; 102675</t>
+          <t>66433; 102068</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>72083; 108917</t>
+          <t>70203; 107005</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>58777; 90631</t>
+          <t>59406; 92870</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>67402; 104484</t>
+          <t>68234; 105588</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>78722; 114762</t>
+          <t>78277; 114412</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>121458; 165267</t>
+          <t>118649; 165441</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>145049; 194569</t>
+          <t>143051; 195524</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>160253; 211878</t>
+          <t>159600; 211541</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>232577; 300228</t>
+          <t>232687; 298110</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>372430; 452990</t>
+          <t>370014; 451923</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>399092; 477614</t>
+          <t>402405; 480831</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>321891; 392999</t>
+          <t>327110; 401198</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>407098; 488123</t>
+          <t>407256; 487599</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>427892; 508433</t>
+          <t>433555; 513658</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>573255; 671909</t>
+          <t>575757; 672395</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>801499; 916580</t>
+          <t>798985; 908902</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>852422; 965569</t>
+          <t>846830; 961595</t>
         </is>
       </c>
     </row>
